--- a/data/20230510-20240924_merged.xlsx
+++ b/data/20230510-20240924_merged.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="15300"/>
+    <workbookView windowWidth="29868" windowHeight="15300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="499">
   <si>
     <t>TIME</t>
   </si>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t>2023年05月10日1200</t>
+  </si>
+  <si>
+    <t>嗯</t>
   </si>
   <si>
     <t>2023年05月11日1200</t>
@@ -1533,7 +1536,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1544,13 +1547,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2018,28 +2014,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2048,118 +2047,115 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2682,8 +2678,8 @@
       <c r="Z2">
         <v>2.05</v>
       </c>
-      <c r="AA2">
-        <v>1.15</v>
+      <c r="AA2" t="s">
+        <v>29</v>
       </c>
       <c r="AB2">
         <v>2.3876772</v>
@@ -2691,7 +2687,7 @@
     </row>
     <row r="3" spans="1:28">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2777,7 +2773,7 @@
     </row>
     <row r="4" spans="1:28">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <v>0.826</v>
@@ -2863,7 +2859,7 @@
     </row>
     <row r="5" spans="1:28">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2949,7 +2945,7 @@
     </row>
     <row r="6" spans="1:28">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3035,7 +3031,7 @@
     </row>
     <row r="7" spans="1:28">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7">
         <v>1.34</v>
@@ -3121,7 +3117,7 @@
     </row>
     <row r="8" spans="1:28">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -3207,7 +3203,7 @@
     </row>
     <row r="9" spans="1:28">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -3293,7 +3289,7 @@
     </row>
     <row r="10" spans="1:28">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -3379,7 +3375,7 @@
     </row>
     <row r="11" spans="1:28">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11">
         <v>1.13</v>
@@ -3465,7 +3461,7 @@
     </row>
     <row r="12" spans="1:28">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12">
         <v>1.67</v>
@@ -3551,7 +3547,7 @@
     </row>
     <row r="13" spans="1:28">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13">
         <v>0.00214</v>
@@ -3637,7 +3633,7 @@
     </row>
     <row r="14" spans="1:28">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14">
         <v>0.89</v>
@@ -3723,7 +3719,7 @@
     </row>
     <row r="15" spans="1:28">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15">
         <v>0.194</v>
@@ -3809,7 +3805,7 @@
     </row>
     <row r="16" spans="1:28">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16">
         <v>1.63</v>
@@ -3895,7 +3891,7 @@
     </row>
     <row r="17" spans="1:28">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -3981,7 +3977,7 @@
     </row>
     <row r="18" spans="1:28">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18">
         <v>1.1</v>
@@ -4067,7 +4063,7 @@
     </row>
     <row r="19" spans="1:28">
       <c r="A19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -4153,7 +4149,7 @@
     </row>
     <row r="20" spans="1:28">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -4239,7 +4235,7 @@
     </row>
     <row r="21" spans="1:28">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B21">
         <v>0.516</v>
@@ -4325,7 +4321,7 @@
     </row>
     <row r="22" spans="1:28">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -4411,7 +4407,7 @@
     </row>
     <row r="23" spans="1:28">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -4497,7 +4493,7 @@
     </row>
     <row r="24" spans="1:28">
       <c r="A24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B24">
         <v>0.0174</v>
@@ -4583,7 +4579,7 @@
     </row>
     <row r="25" spans="1:28">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -4669,7 +4665,7 @@
     </row>
     <row r="26" spans="1:28">
       <c r="A26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B26">
         <v>2.83</v>
@@ -4755,7 +4751,7 @@
     </row>
     <row r="27" spans="1:28">
       <c r="A27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B27">
         <v>2.47</v>
@@ -4841,7 +4837,7 @@
     </row>
     <row r="28" spans="1:28">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B28">
         <v>2.48</v>
@@ -4927,7 +4923,7 @@
     </row>
     <row r="29" spans="1:28">
       <c r="A29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B29">
         <v>3.49</v>
@@ -5013,7 +5009,7 @@
     </row>
     <row r="30" spans="1:28">
       <c r="A30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B30">
         <v>5.9</v>
@@ -5099,7 +5095,7 @@
     </row>
     <row r="31" spans="1:28">
       <c r="A31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B31">
         <v>5.09</v>
@@ -5185,7 +5181,7 @@
     </row>
     <row r="32" spans="1:28">
       <c r="A32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B32">
         <v>4.18</v>
@@ -5271,7 +5267,7 @@
     </row>
     <row r="33" spans="1:28">
       <c r="A33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B33">
         <v>1.94</v>
@@ -5357,7 +5353,7 @@
     </row>
     <row r="34" spans="1:28">
       <c r="A34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B34">
         <v>4.43</v>
@@ -5443,7 +5439,7 @@
     </row>
     <row r="35" spans="1:28">
       <c r="A35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B35">
         <v>5.48</v>
@@ -5529,7 +5525,7 @@
     </row>
     <row r="36" spans="1:28">
       <c r="A36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B36">
         <v>6</v>
@@ -5615,7 +5611,7 @@
     </row>
     <row r="37" spans="1:28">
       <c r="A37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B37">
         <v>4.52</v>
@@ -5701,7 +5697,7 @@
     </row>
     <row r="38" spans="1:28">
       <c r="A38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B38">
         <v>7.42</v>
@@ -5787,7 +5783,7 @@
     </row>
     <row r="39" spans="1:28">
       <c r="A39" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B39">
         <v>6.23</v>
@@ -5873,7 +5869,7 @@
     </row>
     <row r="40" spans="1:28">
       <c r="A40" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B40">
         <v>4.35</v>
@@ -5959,7 +5955,7 @@
     </row>
     <row r="41" spans="1:28">
       <c r="A41" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B41">
         <v>8.53</v>
@@ -6045,7 +6041,7 @@
     </row>
     <row r="42" spans="1:28">
       <c r="A42" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B42">
         <v>3.11</v>
@@ -6131,7 +6127,7 @@
     </row>
     <row r="43" spans="1:28">
       <c r="A43" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B43">
         <v>5.87</v>
@@ -6217,7 +6213,7 @@
     </row>
     <row r="44" spans="1:28">
       <c r="A44" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B44">
         <v>5.76</v>
@@ -6303,7 +6299,7 @@
     </row>
     <row r="45" spans="1:28">
       <c r="A45" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B45">
         <v>7.1</v>
@@ -6389,7 +6385,7 @@
     </row>
     <row r="46" spans="1:28">
       <c r="A46" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B46">
         <v>6.33</v>
@@ -6475,7 +6471,7 @@
     </row>
     <row r="47" spans="1:28">
       <c r="A47" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B47">
         <v>6.77</v>
@@ -6561,7 +6557,7 @@
     </row>
     <row r="48" spans="1:28">
       <c r="A48" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B48">
         <v>7.59</v>
@@ -6647,7 +6643,7 @@
     </row>
     <row r="49" spans="1:28">
       <c r="A49" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B49">
         <v>3.59</v>
@@ -6733,7 +6729,7 @@
     </row>
     <row r="50" spans="1:28">
       <c r="A50" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B50">
         <v>6.95</v>
@@ -6819,7 +6815,7 @@
     </row>
     <row r="51" spans="1:28">
       <c r="A51" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B51">
         <v>0.657</v>
@@ -6905,7 +6901,7 @@
     </row>
     <row r="52" spans="1:28">
       <c r="A52" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B52">
         <v>5.7</v>
@@ -6991,7 +6987,7 @@
     </row>
     <row r="53" spans="1:28">
       <c r="A53" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B53">
         <v>8.14</v>
@@ -7077,7 +7073,7 @@
     </row>
     <row r="54" spans="1:28">
       <c r="A54" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B54">
         <v>9.92</v>
@@ -7163,7 +7159,7 @@
     </row>
     <row r="55" spans="1:28">
       <c r="A55" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -7249,7 +7245,7 @@
     </row>
     <row r="56" spans="1:28">
       <c r="A56" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B56">
         <v>9.64</v>
@@ -7335,7 +7331,7 @@
     </row>
     <row r="57" spans="1:28">
       <c r="A57" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B57">
         <v>8.06</v>
@@ -7421,7 +7417,7 @@
     </row>
     <row r="58" spans="1:28">
       <c r="A58" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B58">
         <v>8.69</v>
@@ -7507,7 +7503,7 @@
     </row>
     <row r="59" spans="1:28">
       <c r="A59" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B59">
         <v>1.26</v>
@@ -7593,7 +7589,7 @@
     </row>
     <row r="60" spans="1:28">
       <c r="A60" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B60">
         <v>4.09</v>
@@ -7679,7 +7675,7 @@
     </row>
     <row r="61" spans="1:28">
       <c r="A61" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B61">
         <v>5</v>
@@ -7765,7 +7761,7 @@
     </row>
     <row r="62" spans="1:28">
       <c r="A62" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B62">
         <v>5.23</v>
@@ -7851,7 +7847,7 @@
     </row>
     <row r="63" spans="1:28">
       <c r="A63" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B63">
         <v>4.47</v>
@@ -7937,7 +7933,7 @@
     </row>
     <row r="64" spans="1:28">
       <c r="A64" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B64">
         <v>2.84</v>
@@ -8023,7 +8019,7 @@
     </row>
     <row r="65" spans="1:28">
       <c r="A65" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B65">
         <v>1.95</v>
@@ -8109,7 +8105,7 @@
     </row>
     <row r="66" spans="1:28">
       <c r="A66" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B66">
         <v>3.96</v>
@@ -8195,7 +8191,7 @@
     </row>
     <row r="67" spans="1:28">
       <c r="A67" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B67">
         <v>2.59</v>
@@ -8281,7 +8277,7 @@
     </row>
     <row r="68" spans="1:28">
       <c r="A68" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B68">
         <v>5.52</v>
@@ -8367,7 +8363,7 @@
     </row>
     <row r="69" spans="1:28">
       <c r="A69" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B69">
         <v>5.01</v>
@@ -8453,7 +8449,7 @@
     </row>
     <row r="70" spans="1:28">
       <c r="A70" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B70">
         <v>11.4</v>
@@ -8539,7 +8535,7 @@
     </row>
     <row r="71" spans="1:28">
       <c r="A71" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B71">
         <v>5.86</v>
@@ -8625,7 +8621,7 @@
     </row>
     <row r="72" spans="1:28">
       <c r="A72" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B72">
         <v>5.34</v>
@@ -8711,7 +8707,7 @@
     </row>
     <row r="73" spans="1:28">
       <c r="A73" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B73">
         <v>2.94</v>
@@ -8797,7 +8793,7 @@
     </row>
     <row r="74" spans="1:28">
       <c r="A74" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B74">
         <v>1.12</v>
@@ -8883,7 +8879,7 @@
     </row>
     <row r="75" spans="1:28">
       <c r="A75" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B75">
         <v>7.11</v>
@@ -8969,7 +8965,7 @@
     </row>
     <row r="76" spans="1:28">
       <c r="A76" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B76">
         <v>5.86</v>
@@ -9055,7 +9051,7 @@
     </row>
     <row r="77" spans="1:28">
       <c r="A77" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B77">
         <v>5.21</v>
@@ -9141,7 +9137,7 @@
     </row>
     <row r="78" spans="1:28">
       <c r="A78" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B78">
         <v>3.85</v>
@@ -9227,7 +9223,7 @@
     </row>
     <row r="79" spans="1:28">
       <c r="A79" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B79">
         <v>2.59</v>
@@ -9313,7 +9309,7 @@
     </row>
     <row r="80" spans="1:28">
       <c r="A80" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B80">
         <v>4.88</v>
@@ -9399,7 +9395,7 @@
     </row>
     <row r="81" spans="1:28">
       <c r="A81" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B81">
         <v>3.67</v>
@@ -9485,7 +9481,7 @@
     </row>
     <row r="82" spans="1:28">
       <c r="A82" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B82">
         <v>2.65</v>
@@ -9571,7 +9567,7 @@
     </row>
     <row r="83" spans="1:28">
       <c r="A83" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B83">
         <v>3.51</v>
@@ -9657,7 +9653,7 @@
     </row>
     <row r="84" spans="1:28">
       <c r="A84" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -9743,7 +9739,7 @@
     </row>
     <row r="85" spans="1:28">
       <c r="A85" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B85">
         <v>3.46</v>
@@ -9829,7 +9825,7 @@
     </row>
     <row r="86" spans="1:28">
       <c r="A86" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B86">
         <v>3.53</v>
@@ -9915,7 +9911,7 @@
     </row>
     <row r="87" spans="1:28">
       <c r="A87" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B87">
         <v>10.1</v>
@@ -10001,7 +9997,7 @@
     </row>
     <row r="88" spans="1:28">
       <c r="A88" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B88">
         <v>5.52</v>
@@ -10087,7 +10083,7 @@
     </row>
     <row r="89" spans="1:28">
       <c r="A89" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B89">
         <v>8.53</v>
@@ -10173,7 +10169,7 @@
     </row>
     <row r="90" spans="1:28">
       <c r="A90" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B90">
         <v>5.85</v>
@@ -10259,7 +10255,7 @@
     </row>
     <row r="91" spans="1:28">
       <c r="A91" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B91">
         <v>5.44</v>
@@ -10345,7 +10341,7 @@
     </row>
     <row r="92" spans="1:28">
       <c r="A92" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B92">
         <v>1.19</v>
@@ -10431,7 +10427,7 @@
     </row>
     <row r="93" spans="1:28">
       <c r="A93" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B93">
         <v>7.67</v>
@@ -10517,7 +10513,7 @@
     </row>
     <row r="94" spans="1:28">
       <c r="A94" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B94">
         <v>4.39</v>
@@ -10603,7 +10599,7 @@
     </row>
     <row r="95" spans="1:28">
       <c r="A95" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B95">
         <v>4.02</v>
@@ -10689,7 +10685,7 @@
     </row>
     <row r="96" spans="1:28">
       <c r="A96" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B96">
         <v>3.13</v>
@@ -10775,7 +10771,7 @@
     </row>
     <row r="97" spans="1:28">
       <c r="A97" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B97">
         <v>7.92</v>
@@ -10861,7 +10857,7 @@
     </row>
     <row r="98" spans="1:28">
       <c r="A98" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B98">
         <v>2.26</v>
@@ -10947,7 +10943,7 @@
     </row>
     <row r="99" spans="1:28">
       <c r="A99" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B99">
         <v>2.24</v>
@@ -11033,7 +11029,7 @@
     </row>
     <row r="100" spans="1:28">
       <c r="A100" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B100">
         <v>0.801</v>
@@ -11119,7 +11115,7 @@
     </row>
     <row r="101" spans="1:28">
       <c r="A101" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B101">
         <v>3.19</v>
@@ -11205,7 +11201,7 @@
     </row>
     <row r="102" spans="1:28">
       <c r="A102" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B102">
         <v>8.69</v>
@@ -11291,7 +11287,7 @@
     </row>
     <row r="103" spans="1:28">
       <c r="A103" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B103">
         <v>3.77</v>
@@ -11377,7 +11373,7 @@
     </row>
     <row r="104" spans="1:28">
       <c r="A104" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B104">
         <v>6.29</v>
@@ -11463,7 +11459,7 @@
     </row>
     <row r="105" spans="1:28">
       <c r="A105" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B105">
         <v>6.06</v>
@@ -11549,7 +11545,7 @@
     </row>
     <row r="106" spans="1:28">
       <c r="A106" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B106">
         <v>6.19</v>
@@ -11635,7 +11631,7 @@
     </row>
     <row r="107" spans="1:28">
       <c r="A107" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B107">
         <v>6.99</v>
@@ -11721,7 +11717,7 @@
     </row>
     <row r="108" spans="1:28">
       <c r="A108" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B108">
         <v>3.94</v>
@@ -11807,7 +11803,7 @@
     </row>
     <row r="109" spans="1:28">
       <c r="A109" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B109">
         <v>2.49</v>
@@ -11893,7 +11889,7 @@
     </row>
     <row r="110" spans="1:28">
       <c r="A110" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B110">
         <v>7.02</v>
@@ -11979,7 +11975,7 @@
     </row>
     <row r="111" spans="1:28">
       <c r="A111" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B111">
         <v>2.09</v>
@@ -12065,7 +12061,7 @@
     </row>
     <row r="112" spans="1:28">
       <c r="A112" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B112">
         <v>8.41</v>
@@ -12151,7 +12147,7 @@
     </row>
     <row r="113" spans="1:28">
       <c r="A113" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B113">
         <v>7.16</v>
@@ -12237,7 +12233,7 @@
     </row>
     <row r="114" spans="1:28">
       <c r="A114" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B114">
         <v>5.17</v>
@@ -12323,7 +12319,7 @@
     </row>
     <row r="115" spans="1:28">
       <c r="A115" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B115">
         <v>6.33</v>
@@ -12404,12 +12400,12 @@
         <v>69.3</v>
       </c>
       <c r="AB115" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="116" spans="1:28">
       <c r="A116" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B116">
         <v>10.4</v>
@@ -12495,7 +12491,7 @@
     </row>
     <row r="117" spans="1:28">
       <c r="A117" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B117">
         <v>7.86</v>
@@ -12581,7 +12577,7 @@
     </row>
     <row r="118" spans="1:28">
       <c r="A118" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B118">
         <v>7.28</v>
@@ -12667,7 +12663,7 @@
     </row>
     <row r="119" spans="1:28">
       <c r="A119" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B119">
         <v>3.42</v>
@@ -12753,7 +12749,7 @@
     </row>
     <row r="120" spans="1:28">
       <c r="A120" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B120">
         <v>6.64</v>
@@ -12839,7 +12835,7 @@
     </row>
     <row r="121" spans="1:28">
       <c r="A121" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B121">
         <v>2.61</v>
@@ -12925,7 +12921,7 @@
     </row>
     <row r="122" spans="1:28">
       <c r="A122" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B122">
         <v>5.73</v>
@@ -13011,7 +13007,7 @@
     </row>
     <row r="123" spans="1:28">
       <c r="A123" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B123">
         <v>6.85</v>
@@ -13097,7 +13093,7 @@
     </row>
     <row r="124" spans="1:28">
       <c r="A124" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B124">
         <v>6.58</v>
@@ -13183,7 +13179,7 @@
     </row>
     <row r="125" spans="1:28">
       <c r="A125" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B125">
         <v>2.77</v>
@@ -13269,7 +13265,7 @@
     </row>
     <row r="126" spans="1:28">
       <c r="A126" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B126">
         <v>4.32</v>
@@ -13355,7 +13351,7 @@
     </row>
     <row r="127" spans="1:28">
       <c r="A127" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B127">
         <v>3.96</v>
@@ -13441,7 +13437,7 @@
     </row>
     <row r="128" spans="1:28">
       <c r="A128" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B128">
         <v>5.12</v>
@@ -13527,7 +13523,7 @@
     </row>
     <row r="129" spans="1:28">
       <c r="A129" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B129">
         <v>8.36</v>
@@ -13613,7 +13609,7 @@
     </row>
     <row r="130" spans="1:28">
       <c r="A130" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B130">
         <v>2.6</v>
@@ -13699,7 +13695,7 @@
     </row>
     <row r="131" spans="1:28">
       <c r="A131" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B131">
         <v>7.27</v>
@@ -13785,7 +13781,7 @@
     </row>
     <row r="132" spans="1:28">
       <c r="A132" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B132">
         <v>8.37</v>
@@ -13871,7 +13867,7 @@
     </row>
     <row r="133" spans="1:28">
       <c r="A133" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B133">
         <v>3.67</v>
@@ -13957,7 +13953,7 @@
     </row>
     <row r="134" spans="1:28">
       <c r="A134" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B134">
         <v>6.16</v>
@@ -14043,7 +14039,7 @@
     </row>
     <row r="135" spans="1:28">
       <c r="A135" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B135">
         <v>1.13</v>
@@ -14129,7 +14125,7 @@
     </row>
     <row r="136" spans="1:28">
       <c r="A136" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B136">
         <v>4.98</v>
@@ -14215,7 +14211,7 @@
     </row>
     <row r="137" spans="1:28">
       <c r="A137" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B137">
         <v>2.51</v>
@@ -14301,7 +14297,7 @@
     </row>
     <row r="138" spans="1:28">
       <c r="A138" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B138">
         <v>6.09</v>
@@ -14387,7 +14383,7 @@
     </row>
     <row r="139" spans="1:28">
       <c r="A139" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B139">
         <v>4.38</v>
@@ -14473,7 +14469,7 @@
     </row>
     <row r="140" spans="1:28">
       <c r="A140" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B140">
         <v>6.17</v>
@@ -14559,7 +14555,7 @@
     </row>
     <row r="141" spans="1:28">
       <c r="A141" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -14645,7 +14641,7 @@
     </row>
     <row r="142" spans="1:28">
       <c r="A142" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B142">
         <v>7.18</v>
@@ -14731,7 +14727,7 @@
     </row>
     <row r="143" spans="1:28">
       <c r="A143" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B143">
         <v>4.91</v>
@@ -14817,7 +14813,7 @@
     </row>
     <row r="144" spans="1:28">
       <c r="A144" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B144">
         <v>2.24</v>
@@ -14903,7 +14899,7 @@
     </row>
     <row r="145" spans="1:28">
       <c r="A145" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B145">
         <v>13.2</v>
@@ -14989,7 +14985,7 @@
     </row>
     <row r="146" spans="1:28">
       <c r="A146" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B146">
         <v>6.5</v>
@@ -15075,7 +15071,7 @@
     </row>
     <row r="147" spans="1:28">
       <c r="A147" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B147">
         <v>0.0405</v>
@@ -15161,7 +15157,7 @@
     </row>
     <row r="148" spans="1:28">
       <c r="A148" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B148">
         <v>2.94</v>
@@ -15247,7 +15243,7 @@
     </row>
     <row r="149" spans="1:28">
       <c r="A149" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B149">
         <v>9.37</v>
@@ -15333,7 +15329,7 @@
     </row>
     <row r="150" spans="1:28">
       <c r="A150" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B150">
         <v>11.6</v>
@@ -15419,7 +15415,7 @@
     </row>
     <row r="151" spans="1:28">
       <c r="A151" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B151">
         <v>4.76</v>
@@ -15505,7 +15501,7 @@
     </row>
     <row r="152" spans="1:28">
       <c r="A152" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B152">
         <v>4.85</v>
@@ -15591,7 +15587,7 @@
     </row>
     <row r="153" spans="1:28">
       <c r="A153" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B153">
         <v>7.83</v>
@@ -15677,7 +15673,7 @@
     </row>
     <row r="154" spans="1:28">
       <c r="A154" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B154">
         <v>10.2</v>
@@ -15763,7 +15759,7 @@
     </row>
     <row r="155" spans="1:28">
       <c r="A155" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B155">
         <v>11.2</v>
@@ -15849,7 +15845,7 @@
     </row>
     <row r="156" spans="1:28">
       <c r="A156" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B156">
         <v>4.52</v>
@@ -15935,7 +15931,7 @@
     </row>
     <row r="157" spans="1:28">
       <c r="A157" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B157">
         <v>0.685</v>
@@ -16021,7 +16017,7 @@
     </row>
     <row r="158" spans="1:28">
       <c r="A158" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B158">
         <v>13.8</v>
@@ -16107,7 +16103,7 @@
     </row>
     <row r="159" spans="1:28">
       <c r="A159" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B159">
         <v>7.4</v>
@@ -16193,7 +16189,7 @@
     </row>
     <row r="160" spans="1:28">
       <c r="A160" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B160">
         <v>5.55</v>
@@ -16279,7 +16275,7 @@
     </row>
     <row r="161" spans="1:28">
       <c r="A161" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B161">
         <v>3.39</v>
@@ -16365,7 +16361,7 @@
     </row>
     <row r="162" spans="1:28">
       <c r="A162" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B162">
         <v>4</v>
@@ -16451,7 +16447,7 @@
     </row>
     <row r="163" spans="1:28">
       <c r="A163" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B163">
         <v>5.16</v>
@@ -16537,7 +16533,7 @@
     </row>
     <row r="164" spans="1:28">
       <c r="A164" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B164">
         <v>5.58</v>
@@ -16623,7 +16619,7 @@
     </row>
     <row r="165" spans="1:28">
       <c r="A165" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B165">
         <v>6.47</v>
@@ -16709,7 +16705,7 @@
     </row>
     <row r="166" spans="1:28">
       <c r="A166" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B166">
         <v>8.4</v>
@@ -16795,7 +16791,7 @@
     </row>
     <row r="167" spans="1:28">
       <c r="A167" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B167">
         <v>7.7</v>
@@ -16881,7 +16877,7 @@
     </row>
     <row r="168" spans="1:28">
       <c r="A168" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B168">
         <v>3.14</v>
@@ -16967,7 +16963,7 @@
     </row>
     <row r="169" spans="1:28">
       <c r="A169" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B169">
         <v>3.46</v>
@@ -17053,7 +17049,7 @@
     </row>
     <row r="170" spans="1:28">
       <c r="A170" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B170">
         <v>8.83</v>
@@ -17139,7 +17135,7 @@
     </row>
     <row r="171" spans="1:28">
       <c r="A171" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B171">
         <v>7.13</v>
@@ -17225,7 +17221,7 @@
     </row>
     <row r="172" spans="1:28">
       <c r="A172" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B172">
         <v>7.56</v>
@@ -17311,7 +17307,7 @@
     </row>
     <row r="173" spans="1:28">
       <c r="A173" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B173">
         <v>8.62</v>
@@ -17392,12 +17388,12 @@
         <v>63.3</v>
       </c>
       <c r="AB173" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="174" spans="1:28">
       <c r="A174" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B174">
         <v>5.36</v>
@@ -17483,7 +17479,7 @@
     </row>
     <row r="175" spans="1:28">
       <c r="A175" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B175">
         <v>5.06</v>
@@ -17569,7 +17565,7 @@
     </row>
     <row r="176" spans="1:28">
       <c r="A176" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B176">
         <v>4.47</v>
@@ -17655,7 +17651,7 @@
     </row>
     <row r="177" spans="1:28">
       <c r="A177" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B177">
         <v>3.58</v>
@@ -17741,7 +17737,7 @@
     </row>
     <row r="178" spans="1:28">
       <c r="A178" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B178">
         <v>7.65</v>
@@ -17827,7 +17823,7 @@
     </row>
     <row r="179" spans="1:28">
       <c r="A179" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B179">
         <v>2.58</v>
@@ -17913,7 +17909,7 @@
     </row>
     <row r="180" spans="1:28">
       <c r="A180" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B180">
         <v>3.82</v>
@@ -17999,7 +17995,7 @@
     </row>
     <row r="181" spans="1:28">
       <c r="A181" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B181">
         <v>8.59</v>
@@ -18085,7 +18081,7 @@
     </row>
     <row r="182" spans="1:28">
       <c r="A182" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -18171,7 +18167,7 @@
     </row>
     <row r="183" spans="1:28">
       <c r="A183" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B183">
         <v>13.4</v>
@@ -18257,7 +18253,7 @@
     </row>
     <row r="184" spans="1:28">
       <c r="A184" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B184">
         <v>7.24</v>
@@ -18343,7 +18339,7 @@
     </row>
     <row r="185" spans="1:28">
       <c r="A185" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B185">
         <v>5.47</v>
@@ -18429,7 +18425,7 @@
     </row>
     <row r="186" spans="1:28">
       <c r="A186" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B186">
         <v>10.3</v>
@@ -18515,7 +18511,7 @@
     </row>
     <row r="187" spans="1:28">
       <c r="A187" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B187">
         <v>5.5</v>
@@ -18601,7 +18597,7 @@
     </row>
     <row r="188" spans="1:28">
       <c r="A188" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B188">
         <v>7.82</v>
@@ -18687,7 +18683,7 @@
     </row>
     <row r="189" spans="1:28">
       <c r="A189" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B189">
         <v>10.2</v>
@@ -18773,7 +18769,7 @@
     </row>
     <row r="190" spans="1:28">
       <c r="A190" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B190">
         <v>9.46</v>
@@ -18859,7 +18855,7 @@
     </row>
     <row r="191" spans="1:28">
       <c r="A191" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B191">
         <v>5.79</v>
@@ -18945,7 +18941,7 @@
     </row>
     <row r="192" spans="1:28">
       <c r="A192" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B192">
         <v>0.606</v>
@@ -19031,7 +19027,7 @@
     </row>
     <row r="193" spans="1:28">
       <c r="A193" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B193">
         <v>4.65</v>
@@ -19117,7 +19113,7 @@
     </row>
     <row r="194" spans="1:28">
       <c r="A194" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B194">
         <v>9.46</v>
@@ -19203,7 +19199,7 @@
     </row>
     <row r="195" spans="1:28">
       <c r="A195" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B195">
         <v>10.6</v>
@@ -19289,7 +19285,7 @@
     </row>
     <row r="196" spans="1:28">
       <c r="A196" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B196">
         <v>11.1</v>
@@ -19375,7 +19371,7 @@
     </row>
     <row r="197" spans="1:28">
       <c r="A197" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B197">
         <v>9.46</v>
@@ -19461,7 +19457,7 @@
     </row>
     <row r="198" spans="1:28">
       <c r="A198" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B198">
         <v>4.64</v>
@@ -19547,7 +19543,7 @@
     </row>
     <row r="199" spans="1:28">
       <c r="A199" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B199">
         <v>7.37</v>
@@ -19633,7 +19629,7 @@
     </row>
     <row r="200" spans="1:28">
       <c r="A200" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B200">
         <v>2.94</v>
@@ -19719,7 +19715,7 @@
     </row>
     <row r="201" spans="1:28">
       <c r="A201" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B201">
         <v>5.78</v>
@@ -19805,7 +19801,7 @@
     </row>
     <row r="202" spans="1:28">
       <c r="A202" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B202">
         <v>5.92</v>
@@ -19891,7 +19887,7 @@
     </row>
     <row r="203" spans="1:28">
       <c r="A203" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B203">
         <v>4.26</v>
@@ -19977,7 +19973,7 @@
     </row>
     <row r="204" spans="1:28">
       <c r="A204" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B204">
         <v>7.66</v>
@@ -20063,7 +20059,7 @@
     </row>
     <row r="205" spans="1:28">
       <c r="A205" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B205">
         <v>3.44</v>
@@ -20149,7 +20145,7 @@
     </row>
     <row r="206" spans="1:28">
       <c r="A206" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B206">
         <v>7.61</v>
@@ -20235,7 +20231,7 @@
     </row>
     <row r="207" spans="1:28">
       <c r="A207" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B207">
         <v>4.19</v>
@@ -20321,7 +20317,7 @@
     </row>
     <row r="208" spans="1:28">
       <c r="A208" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B208">
         <v>4.06</v>
@@ -20407,7 +20403,7 @@
     </row>
     <row r="209" spans="1:28">
       <c r="A209" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B209">
         <v>8.4</v>
@@ -20493,7 +20489,7 @@
     </row>
     <row r="210" spans="1:28">
       <c r="A210" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B210">
         <v>8.32</v>
@@ -20579,7 +20575,7 @@
     </row>
     <row r="211" spans="1:28">
       <c r="A211" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B211">
         <v>4.91</v>
@@ -20665,7 +20661,7 @@
     </row>
     <row r="212" spans="1:28">
       <c r="A212" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B212">
         <v>9.84</v>
@@ -20751,7 +20747,7 @@
     </row>
     <row r="213" spans="1:28">
       <c r="A213" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B213">
         <v>3.89</v>
@@ -20837,7 +20833,7 @@
     </row>
     <row r="214" spans="1:28">
       <c r="A214" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B214">
         <v>3.74</v>
@@ -20923,7 +20919,7 @@
     </row>
     <row r="215" spans="1:28">
       <c r="A215" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B215">
         <v>7.81</v>
@@ -21009,7 +21005,7 @@
     </row>
     <row r="216" spans="1:28">
       <c r="A216" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B216">
         <v>1.91</v>
@@ -21095,7 +21091,7 @@
     </row>
     <row r="217" spans="1:28">
       <c r="A217" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B217">
         <v>0</v>
@@ -21181,7 +21177,7 @@
     </row>
     <row r="218" spans="1:28">
       <c r="A218" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B218">
         <v>5.13</v>
@@ -21267,7 +21263,7 @@
     </row>
     <row r="219" spans="1:28">
       <c r="A219" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B219">
         <v>5.8</v>
@@ -21353,7 +21349,7 @@
     </row>
     <row r="220" spans="1:28">
       <c r="A220" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B220">
         <v>5.46</v>
@@ -21439,7 +21435,7 @@
     </row>
     <row r="221" spans="1:28">
       <c r="A221" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B221">
         <v>4.54</v>
@@ -21525,7 +21521,7 @@
     </row>
     <row r="222" spans="1:28">
       <c r="A222" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B222">
         <v>5.21</v>
@@ -21611,7 +21607,7 @@
     </row>
     <row r="223" spans="1:28">
       <c r="A223" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B223">
         <v>3.65</v>
@@ -21697,7 +21693,7 @@
     </row>
     <row r="224" spans="1:28">
       <c r="A224" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B224">
         <v>4.51</v>
@@ -21783,7 +21779,7 @@
     </row>
     <row r="225" spans="1:28">
       <c r="A225" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B225">
         <v>5.81</v>
@@ -21869,7 +21865,7 @@
     </row>
     <row r="226" spans="1:28">
       <c r="A226" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B226">
         <v>3.82</v>
@@ -21955,7 +21951,7 @@
     </row>
     <row r="227" spans="1:28">
       <c r="A227" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B227">
         <v>3.02</v>
@@ -22041,7 +22037,7 @@
     </row>
     <row r="228" spans="1:28">
       <c r="A228" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B228">
         <v>4.62</v>
@@ -22127,7 +22123,7 @@
     </row>
     <row r="229" spans="1:28">
       <c r="A229" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B229">
         <v>11.6</v>
@@ -22213,7 +22209,7 @@
     </row>
     <row r="230" spans="1:28">
       <c r="A230" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B230">
         <v>6.5</v>
@@ -22299,7 +22295,7 @@
     </row>
     <row r="231" spans="1:28">
       <c r="A231" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B231">
         <v>4.64</v>
@@ -22385,7 +22381,7 @@
     </row>
     <row r="232" spans="1:28">
       <c r="A232" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B232">
         <v>6.84</v>
@@ -22471,7 +22467,7 @@
     </row>
     <row r="233" spans="1:28">
       <c r="A233" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B233">
         <v>9.45</v>
@@ -22557,7 +22553,7 @@
     </row>
     <row r="234" spans="1:28">
       <c r="A234" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B234">
         <v>9.61</v>
@@ -22643,7 +22639,7 @@
     </row>
     <row r="235" spans="1:28">
       <c r="A235" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B235">
         <v>4.74</v>
@@ -22729,7 +22725,7 @@
     </row>
     <row r="236" spans="1:28">
       <c r="A236" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B236">
         <v>4.31</v>
@@ -22815,7 +22811,7 @@
     </row>
     <row r="237" spans="1:28">
       <c r="A237" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B237">
         <v>4.84</v>
@@ -22896,12 +22892,12 @@
         <v>78</v>
       </c>
       <c r="AB237" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="238" spans="1:28">
       <c r="A238" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B238">
         <v>12.3</v>
@@ -22987,7 +22983,7 @@
     </row>
     <row r="239" spans="1:28">
       <c r="A239" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B239">
         <v>5.84</v>
@@ -23073,7 +23069,7 @@
     </row>
     <row r="240" spans="1:28">
       <c r="A240" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B240">
         <v>3.64</v>
@@ -23159,7 +23155,7 @@
     </row>
     <row r="241" spans="1:28">
       <c r="A241" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B241">
         <v>4.47</v>
@@ -23245,7 +23241,7 @@
     </row>
     <row r="242" spans="1:28">
       <c r="A242" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B242">
         <v>4.59</v>
@@ -23331,7 +23327,7 @@
     </row>
     <row r="243" spans="1:28">
       <c r="A243" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B243">
         <v>4.73</v>
@@ -23417,7 +23413,7 @@
     </row>
     <row r="244" spans="1:28">
       <c r="A244" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B244">
         <v>5.29</v>
@@ -23503,7 +23499,7 @@
     </row>
     <row r="245" spans="1:28">
       <c r="A245" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B245">
         <v>4.47</v>
@@ -23589,7 +23585,7 @@
     </row>
     <row r="246" spans="1:28">
       <c r="A246" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B246">
         <v>5.71</v>
@@ -23675,7 +23671,7 @@
     </row>
     <row r="247" spans="1:28">
       <c r="A247" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B247">
         <v>1.87</v>
@@ -23761,7 +23757,7 @@
     </row>
     <row r="248" spans="1:28">
       <c r="A248" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B248">
         <v>7.61</v>
@@ -23847,7 +23843,7 @@
     </row>
     <row r="249" spans="1:28">
       <c r="A249" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B249">
         <v>8.65</v>
@@ -23933,7 +23929,7 @@
     </row>
     <row r="250" spans="1:28">
       <c r="A250" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B250">
         <v>4.96</v>
@@ -24019,7 +24015,7 @@
     </row>
     <row r="251" spans="1:28">
       <c r="A251" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B251">
         <v>4.49</v>
@@ -24105,7 +24101,7 @@
     </row>
     <row r="252" spans="1:28">
       <c r="A252" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B252">
         <v>3.97</v>
@@ -24191,7 +24187,7 @@
     </row>
     <row r="253" spans="1:28">
       <c r="A253" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B253">
         <v>6.34</v>
@@ -24277,7 +24273,7 @@
     </row>
     <row r="254" spans="1:28">
       <c r="A254" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B254">
         <v>4.33</v>
@@ -24363,7 +24359,7 @@
     </row>
     <row r="255" spans="1:28">
       <c r="A255" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B255">
         <v>0.321</v>
@@ -24449,7 +24445,7 @@
     </row>
     <row r="256" spans="1:28">
       <c r="A256" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B256">
         <v>8.36</v>
@@ -24535,7 +24531,7 @@
     </row>
     <row r="257" spans="1:28">
       <c r="A257" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B257">
         <v>8.22</v>
@@ -24621,7 +24617,7 @@
     </row>
     <row r="258" spans="1:28">
       <c r="A258" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B258">
         <v>8.18</v>
@@ -24707,7 +24703,7 @@
     </row>
     <row r="259" spans="1:28">
       <c r="A259" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B259">
         <v>9.03</v>
@@ -24793,7 +24789,7 @@
     </row>
     <row r="260" spans="1:28">
       <c r="A260" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B260">
         <v>3.84</v>
@@ -24879,7 +24875,7 @@
     </row>
     <row r="261" spans="1:28">
       <c r="A261" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B261">
         <v>9.22</v>
@@ -24965,7 +24961,7 @@
     </row>
     <row r="262" spans="1:28">
       <c r="A262" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B262">
         <v>4.61</v>
@@ -25051,7 +25047,7 @@
     </row>
     <row r="263" spans="1:28">
       <c r="A263" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B263">
         <v>2.24</v>
@@ -25137,7 +25133,7 @@
     </row>
     <row r="264" spans="1:28">
       <c r="A264" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B264">
         <v>4.2</v>
@@ -25223,7 +25219,7 @@
     </row>
     <row r="265" spans="1:28">
       <c r="A265" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B265">
         <v>10.1</v>
@@ -25309,7 +25305,7 @@
     </row>
     <row r="266" spans="1:28">
       <c r="A266" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B266">
         <v>7.12</v>
@@ -25395,7 +25391,7 @@
     </row>
     <row r="267" spans="1:28">
       <c r="A267" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B267">
         <v>5.72</v>
@@ -25481,7 +25477,7 @@
     </row>
     <row r="268" spans="1:28">
       <c r="A268" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B268">
         <v>5.04</v>
@@ -25567,7 +25563,7 @@
     </row>
     <row r="269" spans="1:28">
       <c r="A269" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B269">
         <v>3.74</v>
@@ -25653,7 +25649,7 @@
     </row>
     <row r="270" spans="1:28">
       <c r="A270" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B270">
         <v>8.06</v>
@@ -25739,7 +25735,7 @@
     </row>
     <row r="271" spans="1:28">
       <c r="A271" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B271">
         <v>7.43</v>
@@ -25825,7 +25821,7 @@
     </row>
     <row r="272" spans="1:28">
       <c r="A272" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B272">
         <v>3.11</v>
@@ -25911,7 +25907,7 @@
     </row>
     <row r="273" spans="1:28">
       <c r="A273" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B273">
         <v>2.3</v>
@@ -25997,7 +25993,7 @@
     </row>
     <row r="274" spans="1:28">
       <c r="A274" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B274">
         <v>9.03</v>
@@ -26083,7 +26079,7 @@
     </row>
     <row r="275" spans="1:28">
       <c r="A275" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B275">
         <v>7.9</v>
@@ -26169,7 +26165,7 @@
     </row>
     <row r="276" spans="1:28">
       <c r="A276" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B276">
         <v>7.21</v>
@@ -26255,7 +26251,7 @@
     </row>
     <row r="277" spans="1:28">
       <c r="A277" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B277">
         <v>7.1</v>
@@ -26341,7 +26337,7 @@
     </row>
     <row r="278" spans="1:28">
       <c r="A278" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B278">
         <v>4.01</v>
@@ -26427,7 +26423,7 @@
     </row>
     <row r="279" spans="1:28">
       <c r="A279" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B279">
         <v>4.67</v>
@@ -26513,7 +26509,7 @@
     </row>
     <row r="280" spans="1:28">
       <c r="A280" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B280">
         <v>4.3</v>
@@ -26599,7 +26595,7 @@
     </row>
     <row r="281" spans="1:28">
       <c r="A281" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B281">
         <v>6.11</v>
@@ -26685,7 +26681,7 @@
     </row>
     <row r="282" spans="1:28">
       <c r="A282" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B282">
         <v>5.1</v>
@@ -26771,7 +26767,7 @@
     </row>
     <row r="283" spans="1:28">
       <c r="A283" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B283">
         <v>1.55</v>
@@ -26857,7 +26853,7 @@
     </row>
     <row r="284" spans="1:28">
       <c r="A284" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B284">
         <v>5.82</v>
@@ -26943,7 +26939,7 @@
     </row>
     <row r="285" spans="1:28">
       <c r="A285" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B285">
         <v>6.45</v>
@@ -27029,7 +27025,7 @@
     </row>
     <row r="286" spans="1:28">
       <c r="A286" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B286">
         <v>3.26</v>
@@ -27115,7 +27111,7 @@
     </row>
     <row r="287" spans="1:28">
       <c r="A287" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B287">
         <v>3.2</v>
@@ -27201,7 +27197,7 @@
     </row>
     <row r="288" spans="1:28">
       <c r="A288" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B288">
         <v>6.79</v>
@@ -27287,7 +27283,7 @@
     </row>
     <row r="289" spans="1:28">
       <c r="A289" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B289">
         <v>7.63</v>
@@ -27373,7 +27369,7 @@
     </row>
     <row r="290" spans="1:28">
       <c r="A290" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B290">
         <v>4.28</v>
@@ -27459,7 +27455,7 @@
     </row>
     <row r="291" spans="1:28">
       <c r="A291" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B291">
         <v>7.02</v>
@@ -27545,7 +27541,7 @@
     </row>
     <row r="292" spans="1:28">
       <c r="A292" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B292">
         <v>1.39</v>
@@ -27631,7 +27627,7 @@
     </row>
     <row r="293" spans="1:28">
       <c r="A293" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B293">
         <v>4.64</v>
@@ -27717,7 +27713,7 @@
     </row>
     <row r="294" spans="1:28">
       <c r="A294" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B294">
         <v>12.1</v>
@@ -27803,7 +27799,7 @@
     </row>
     <row r="295" spans="1:28">
       <c r="A295" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B295">
         <v>6.45</v>
@@ -27889,7 +27885,7 @@
     </row>
     <row r="296" spans="1:28">
       <c r="A296" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B296">
         <v>4.88</v>
@@ -27975,7 +27971,7 @@
     </row>
     <row r="297" spans="1:28">
       <c r="A297" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B297">
         <v>8.41</v>
@@ -28061,7 +28057,7 @@
     </row>
     <row r="298" spans="1:28">
       <c r="A298" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B298">
         <v>4.57</v>
@@ -28147,7 +28143,7 @@
     </row>
     <row r="299" spans="1:28">
       <c r="A299" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B299">
         <v>1.62</v>
@@ -28233,7 +28229,7 @@
     </row>
     <row r="300" spans="1:28">
       <c r="A300" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B300">
         <v>9.1</v>
@@ -28319,7 +28315,7 @@
     </row>
     <row r="301" spans="1:28">
       <c r="A301" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B301">
         <v>10.9</v>
@@ -28405,7 +28401,7 @@
     </row>
     <row r="302" spans="1:28">
       <c r="A302" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B302">
         <v>3.25</v>
@@ -28491,7 +28487,7 @@
     </row>
     <row r="303" spans="1:28">
       <c r="A303" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B303">
         <v>7.75</v>
@@ -28577,7 +28573,7 @@
     </row>
     <row r="304" spans="1:28">
       <c r="A304" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B304">
         <v>4.06</v>
@@ -28663,7 +28659,7 @@
     </row>
     <row r="305" spans="1:28">
       <c r="A305" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B305">
         <v>1.15</v>
@@ -28749,7 +28745,7 @@
     </row>
     <row r="306" spans="1:28">
       <c r="A306" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B306">
         <v>8.13</v>
@@ -28835,7 +28831,7 @@
     </row>
     <row r="307" spans="1:28">
       <c r="A307" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B307">
         <v>7.24</v>
@@ -28921,7 +28917,7 @@
     </row>
     <row r="308" spans="1:28">
       <c r="A308" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B308">
         <v>8.51</v>
@@ -29007,7 +29003,7 @@
     </row>
     <row r="309" spans="1:28">
       <c r="A309" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -29093,7 +29089,7 @@
     </row>
     <row r="310" spans="1:28">
       <c r="A310" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B310">
         <v>6.04</v>
@@ -29179,7 +29175,7 @@
     </row>
     <row r="311" spans="1:28">
       <c r="A311" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B311">
         <v>7.7</v>
@@ -29265,7 +29261,7 @@
     </row>
     <row r="312" spans="1:28">
       <c r="A312" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B312">
         <v>2.2</v>
@@ -29351,7 +29347,7 @@
     </row>
     <row r="313" spans="1:28">
       <c r="A313" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B313">
         <v>6.24</v>
@@ -29437,7 +29433,7 @@
     </row>
     <row r="314" spans="1:28">
       <c r="A314" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B314">
         <v>5.92</v>
@@ -29523,7 +29519,7 @@
     </row>
     <row r="315" spans="1:28">
       <c r="A315" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B315">
         <v>9.56</v>
@@ -29609,7 +29605,7 @@
     </row>
     <row r="316" spans="1:28">
       <c r="A316" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B316">
         <v>8.46</v>
@@ -29695,7 +29691,7 @@
     </row>
     <row r="317" spans="1:28">
       <c r="A317" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B317">
         <v>3.14</v>
@@ -29781,7 +29777,7 @@
     </row>
     <row r="318" spans="1:28">
       <c r="A318" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B318">
         <v>8.78</v>
@@ -29867,7 +29863,7 @@
     </row>
     <row r="319" spans="1:28">
       <c r="A319" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B319">
         <v>5.35</v>
@@ -29953,7 +29949,7 @@
     </row>
     <row r="320" spans="1:28">
       <c r="A320" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B320">
         <v>7.27</v>
@@ -30039,7 +30035,7 @@
     </row>
     <row r="321" spans="1:28">
       <c r="A321" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B321">
         <v>3.24</v>
@@ -30125,7 +30121,7 @@
     </row>
     <row r="322" spans="1:28">
       <c r="A322" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B322">
         <v>1.74</v>
@@ -30211,7 +30207,7 @@
     </row>
     <row r="323" spans="1:28">
       <c r="A323" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B323">
         <v>6.03</v>
@@ -30297,7 +30293,7 @@
     </row>
     <row r="324" spans="1:28">
       <c r="A324" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B324">
         <v>5.62</v>
@@ -30383,7 +30379,7 @@
     </row>
     <row r="325" spans="1:28">
       <c r="A325" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B325">
         <v>4.32</v>
@@ -30469,7 +30465,7 @@
     </row>
     <row r="326" spans="1:28">
       <c r="A326" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B326">
         <v>4.56</v>
@@ -30555,7 +30551,7 @@
     </row>
     <row r="327" spans="1:28">
       <c r="A327" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B327">
         <v>4.28</v>
@@ -30641,7 +30637,7 @@
     </row>
     <row r="328" spans="1:28">
       <c r="A328" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B328">
         <v>8.49</v>
@@ -30727,7 +30723,7 @@
     </row>
     <row r="329" spans="1:28">
       <c r="A329" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B329">
         <v>3.82</v>
@@ -30813,7 +30809,7 @@
     </row>
     <row r="330" spans="1:28">
       <c r="A330" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B330">
         <v>8.78</v>
@@ -30899,7 +30895,7 @@
     </row>
     <row r="331" spans="1:28">
       <c r="A331" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B331">
         <v>9.78</v>
@@ -30985,7 +30981,7 @@
     </row>
     <row r="332" spans="1:28">
       <c r="A332" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B332">
         <v>3.45</v>
@@ -31071,7 +31067,7 @@
     </row>
     <row r="333" spans="1:28">
       <c r="A333" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B333">
         <v>5.59</v>
@@ -31157,7 +31153,7 @@
     </row>
     <row r="334" spans="1:28">
       <c r="A334" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B334">
         <v>8.39</v>
@@ -31243,7 +31239,7 @@
     </row>
     <row r="335" spans="1:28">
       <c r="A335" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B335">
         <v>6.97</v>
@@ -31329,7 +31325,7 @@
     </row>
     <row r="336" spans="1:28">
       <c r="A336" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B336">
         <v>9.46</v>
@@ -31415,7 +31411,7 @@
     </row>
     <row r="337" spans="1:28">
       <c r="A337" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B337">
         <v>2.37</v>
@@ -31501,7 +31497,7 @@
     </row>
     <row r="338" spans="1:28">
       <c r="A338" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B338">
         <v>0</v>
@@ -31587,7 +31583,7 @@
     </row>
     <row r="339" spans="1:28">
       <c r="A339" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B339">
         <v>6.94</v>
@@ -31673,7 +31669,7 @@
     </row>
     <row r="340" spans="1:28">
       <c r="A340" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B340">
         <v>4.34</v>
@@ -31759,7 +31755,7 @@
     </row>
     <row r="341" spans="1:28">
       <c r="A341" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B341">
         <v>4.58</v>
@@ -31845,7 +31841,7 @@
     </row>
     <row r="342" spans="1:28">
       <c r="A342" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B342">
         <v>3.86</v>
@@ -31931,7 +31927,7 @@
     </row>
     <row r="343" spans="1:28">
       <c r="A343" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B343">
         <v>6.36</v>
@@ -32017,7 +32013,7 @@
     </row>
     <row r="344" spans="1:28">
       <c r="A344" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B344">
         <v>4.09</v>
@@ -32103,7 +32099,7 @@
     </row>
     <row r="345" spans="1:28">
       <c r="A345" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B345">
         <v>6.07</v>
@@ -32189,7 +32185,7 @@
     </row>
     <row r="346" spans="1:28">
       <c r="A346" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B346">
         <v>12</v>
@@ -32275,7 +32271,7 @@
     </row>
     <row r="347" spans="1:28">
       <c r="A347" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B347">
         <v>7.13</v>
@@ -32361,7 +32357,7 @@
     </row>
     <row r="348" spans="1:28">
       <c r="A348" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B348">
         <v>5.93</v>
@@ -32447,7 +32443,7 @@
     </row>
     <row r="349" spans="1:28">
       <c r="A349" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B349">
         <v>13.4</v>
@@ -32533,7 +32529,7 @@
     </row>
     <row r="350" spans="1:28">
       <c r="A350" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B350">
         <v>4.75</v>
@@ -32619,7 +32615,7 @@
     </row>
     <row r="351" spans="1:28">
       <c r="A351" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B351">
         <v>9.36</v>
@@ -32705,7 +32701,7 @@
     </row>
     <row r="352" spans="1:28">
       <c r="A352" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B352">
         <v>3.78</v>
@@ -32791,7 +32787,7 @@
     </row>
     <row r="353" spans="1:28">
       <c r="A353" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B353">
         <v>5.32</v>
@@ -32877,7 +32873,7 @@
     </row>
     <row r="354" spans="1:28">
       <c r="A354" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B354">
         <v>8.25</v>
@@ -32963,7 +32959,7 @@
     </row>
     <row r="355" spans="1:28">
       <c r="A355" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B355">
         <v>1.27</v>
@@ -33049,7 +33045,7 @@
     </row>
     <row r="356" spans="1:28">
       <c r="A356" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B356">
         <v>4.39</v>
@@ -33135,7 +33131,7 @@
     </row>
     <row r="357" spans="1:28">
       <c r="A357" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B357">
         <v>7.78</v>
@@ -33221,7 +33217,7 @@
     </row>
     <row r="358" spans="1:28">
       <c r="A358" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B358">
         <v>10.9</v>
@@ -33302,12 +33298,12 @@
         <v>78.8</v>
       </c>
       <c r="AB358" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="359" spans="1:28">
       <c r="A359" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B359">
         <v>3.71</v>
@@ -33393,7 +33389,7 @@
     </row>
     <row r="360" spans="1:28">
       <c r="A360" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B360">
         <v>5.51</v>
@@ -33479,7 +33475,7 @@
     </row>
     <row r="361" spans="1:28">
       <c r="A361" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B361">
         <v>1.3</v>
@@ -33565,7 +33561,7 @@
     </row>
     <row r="362" spans="1:28">
       <c r="A362" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B362">
         <v>5.58</v>
@@ -33651,7 +33647,7 @@
     </row>
     <row r="363" spans="1:28">
       <c r="A363" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B363">
         <v>4.29</v>
@@ -33737,7 +33733,7 @@
     </row>
     <row r="364" spans="1:28">
       <c r="A364" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B364">
         <v>2.27</v>
@@ -33823,7 +33819,7 @@
     </row>
     <row r="365" spans="1:28">
       <c r="A365" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B365">
         <v>5.99</v>
@@ -33909,7 +33905,7 @@
     </row>
     <row r="366" spans="1:28">
       <c r="A366" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B366">
         <v>4.56</v>
@@ -33995,7 +33991,7 @@
     </row>
     <row r="367" spans="1:28">
       <c r="A367" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B367">
         <v>6.03</v>
@@ -34081,7 +34077,7 @@
     </row>
     <row r="368" spans="1:28">
       <c r="A368" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B368">
         <v>8.32</v>
@@ -34167,7 +34163,7 @@
     </row>
     <row r="369" spans="1:28">
       <c r="A369" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B369">
         <v>2.93</v>
@@ -34253,7 +34249,7 @@
     </row>
     <row r="370" spans="1:28">
       <c r="A370" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B370">
         <v>3.19</v>
@@ -34339,7 +34335,7 @@
     </row>
     <row r="371" spans="1:28">
       <c r="A371" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B371">
         <v>4.37</v>
@@ -34425,7 +34421,7 @@
     </row>
     <row r="372" spans="1:28">
       <c r="A372" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B372">
         <v>12.9</v>
@@ -34511,7 +34507,7 @@
     </row>
     <row r="373" spans="1:28">
       <c r="A373" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B373">
         <v>11.2</v>
@@ -34597,7 +34593,7 @@
     </row>
     <row r="374" spans="1:28">
       <c r="A374" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B374">
         <v>9.58</v>
@@ -34683,7 +34679,7 @@
     </row>
     <row r="375" spans="1:28">
       <c r="A375" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B375">
         <v>4</v>
@@ -34769,7 +34765,7 @@
     </row>
     <row r="376" spans="1:28">
       <c r="A376" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B376">
         <v>6.71</v>
@@ -34855,7 +34851,7 @@
     </row>
     <row r="377" spans="1:28">
       <c r="A377" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B377">
         <v>8.6</v>
@@ -34941,7 +34937,7 @@
     </row>
     <row r="378" spans="1:28">
       <c r="A378" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B378">
         <v>2.78</v>
@@ -35027,7 +35023,7 @@
     </row>
     <row r="379" spans="1:28">
       <c r="A379" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B379">
         <v>8.94</v>
@@ -35113,7 +35109,7 @@
     </row>
     <row r="380" spans="1:28">
       <c r="A380" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B380">
         <v>6.18</v>
@@ -35199,7 +35195,7 @@
     </row>
     <row r="381" spans="1:28">
       <c r="A381" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B381">
         <v>4.58</v>
@@ -35285,7 +35281,7 @@
     </row>
     <row r="382" spans="1:28">
       <c r="A382" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B382">
         <v>6.22</v>
@@ -35371,7 +35367,7 @@
     </row>
     <row r="383" spans="1:28">
       <c r="A383" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B383">
         <v>3.84</v>
@@ -35457,7 +35453,7 @@
     </row>
     <row r="384" spans="1:28">
       <c r="A384" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B384">
         <v>7.99</v>
@@ -35543,7 +35539,7 @@
     </row>
     <row r="385" spans="1:28">
       <c r="A385" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B385">
         <v>5.15</v>
@@ -35629,7 +35625,7 @@
     </row>
     <row r="386" spans="1:28">
       <c r="A386" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B386">
         <v>5.06</v>
@@ -35715,7 +35711,7 @@
     </row>
     <row r="387" spans="1:28">
       <c r="A387" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B387">
         <v>6.92</v>
@@ -35801,7 +35797,7 @@
     </row>
     <row r="388" spans="1:28">
       <c r="A388" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B388">
         <v>6.56</v>
@@ -35887,7 +35883,7 @@
     </row>
     <row r="389" spans="1:28">
       <c r="A389" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B389">
         <v>5.36</v>
@@ -35973,7 +35969,7 @@
     </row>
     <row r="390" spans="1:28">
       <c r="A390" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B390">
         <v>9.26</v>
@@ -36059,7 +36055,7 @@
     </row>
     <row r="391" spans="1:28">
       <c r="A391" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B391">
         <v>8.59</v>
@@ -36145,7 +36141,7 @@
     </row>
     <row r="392" spans="1:28">
       <c r="A392" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B392">
         <v>5.52</v>
@@ -36231,7 +36227,7 @@
     </row>
     <row r="393" spans="1:28">
       <c r="A393" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B393">
         <v>2.26</v>
@@ -36317,7 +36313,7 @@
     </row>
     <row r="394" spans="1:28">
       <c r="A394" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B394">
         <v>2.13</v>
@@ -36403,7 +36399,7 @@
     </row>
     <row r="395" spans="1:28">
       <c r="A395" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B395">
         <v>11</v>
@@ -36489,7 +36485,7 @@
     </row>
     <row r="396" spans="1:28">
       <c r="A396" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B396">
         <v>10.7</v>
@@ -36575,7 +36571,7 @@
     </row>
     <row r="397" spans="1:28">
       <c r="A397" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B397">
         <v>3.47</v>
@@ -36661,7 +36657,7 @@
     </row>
     <row r="398" spans="1:28">
       <c r="A398" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B398">
         <v>3.85</v>
@@ -36747,7 +36743,7 @@
     </row>
     <row r="399" spans="1:28">
       <c r="A399" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B399">
         <v>10.1</v>
@@ -36833,7 +36829,7 @@
     </row>
     <row r="400" spans="1:28">
       <c r="A400" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B400">
         <v>6.7</v>
@@ -36919,7 +36915,7 @@
     </row>
     <row r="401" spans="1:28">
       <c r="A401" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B401">
         <v>6.57</v>
@@ -37005,7 +37001,7 @@
     </row>
     <row r="402" spans="1:28">
       <c r="A402" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B402">
         <v>8.95</v>
@@ -37091,7 +37087,7 @@
     </row>
     <row r="403" spans="1:28">
       <c r="A403" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B403">
         <v>9.39</v>
@@ -37177,7 +37173,7 @@
     </row>
     <row r="404" spans="1:28">
       <c r="A404" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B404">
         <v>10</v>
@@ -37263,7 +37259,7 @@
     </row>
     <row r="405" spans="1:28">
       <c r="A405" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B405">
         <v>8.33</v>
@@ -37349,7 +37345,7 @@
     </row>
     <row r="406" spans="1:28">
       <c r="A406" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B406">
         <v>5.62</v>
@@ -37435,7 +37431,7 @@
     </row>
     <row r="407" spans="1:28">
       <c r="A407" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B407">
         <v>2.24</v>
@@ -37521,7 +37517,7 @@
     </row>
     <row r="408" spans="1:28">
       <c r="A408" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B408">
         <v>6.2</v>
@@ -37607,7 +37603,7 @@
     </row>
     <row r="409" spans="1:28">
       <c r="A409" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B409">
         <v>9.13</v>
@@ -37693,7 +37689,7 @@
     </row>
     <row r="410" spans="1:28">
       <c r="A410" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B410">
         <v>7.66</v>
@@ -37779,7 +37775,7 @@
     </row>
     <row r="411" spans="1:28">
       <c r="A411" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B411">
         <v>7.66</v>
@@ -37865,7 +37861,7 @@
     </row>
     <row r="412" spans="1:28">
       <c r="A412" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B412">
         <v>5.13</v>
@@ -37951,7 +37947,7 @@
     </row>
     <row r="413" spans="1:28">
       <c r="A413" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B413">
         <v>9.9</v>
@@ -38037,7 +38033,7 @@
     </row>
     <row r="414" spans="1:28">
       <c r="A414" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B414">
         <v>7.19</v>
@@ -38123,7 +38119,7 @@
     </row>
     <row r="415" spans="1:28">
       <c r="A415" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B415">
         <v>5.54</v>
@@ -38209,7 +38205,7 @@
     </row>
     <row r="416" spans="1:28">
       <c r="A416" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B416">
         <v>3.68</v>
@@ -38295,7 +38291,7 @@
     </row>
     <row r="417" spans="1:28">
       <c r="A417" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B417">
         <v>5.2</v>
@@ -38381,7 +38377,7 @@
     </row>
     <row r="418" spans="1:28">
       <c r="A418" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B418">
         <v>5.85</v>
@@ -38467,7 +38463,7 @@
     </row>
     <row r="419" spans="1:28">
       <c r="A419" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B419">
         <v>5.3</v>
@@ -38553,7 +38549,7 @@
     </row>
     <row r="420" spans="1:28">
       <c r="A420" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B420">
         <v>2.19</v>
@@ -38639,7 +38635,7 @@
     </row>
     <row r="421" spans="1:28">
       <c r="A421" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B421">
         <v>10.3</v>
@@ -38725,7 +38721,7 @@
     </row>
     <row r="422" spans="1:28">
       <c r="A422" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B422">
         <v>9.98</v>
@@ -38811,7 +38807,7 @@
     </row>
     <row r="423" spans="1:28">
       <c r="A423" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B423">
         <v>8.07</v>
@@ -38897,7 +38893,7 @@
     </row>
     <row r="424" spans="1:28">
       <c r="A424" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B424">
         <v>6.46</v>
@@ -38983,7 +38979,7 @@
     </row>
     <row r="425" spans="1:28">
       <c r="A425" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B425">
         <v>5.28</v>
@@ -39069,7 +39065,7 @@
     </row>
     <row r="426" spans="1:28">
       <c r="A426" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B426">
         <v>5.58</v>
@@ -39155,7 +39151,7 @@
     </row>
     <row r="427" spans="1:28">
       <c r="A427" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B427">
         <v>5.1</v>
@@ -39241,7 +39237,7 @@
     </row>
     <row r="428" spans="1:28">
       <c r="A428" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B428">
         <v>7.09</v>
@@ -39327,7 +39323,7 @@
     </row>
     <row r="429" spans="1:28">
       <c r="A429" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B429">
         <v>0.548</v>
@@ -39413,7 +39409,7 @@
     </row>
     <row r="430" spans="1:28">
       <c r="A430" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B430">
         <v>11.4</v>
@@ -39499,7 +39495,7 @@
     </row>
     <row r="431" spans="1:28">
       <c r="A431" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B431">
         <v>9.11</v>
@@ -39585,7 +39581,7 @@
     </row>
     <row r="432" spans="1:28">
       <c r="A432" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B432">
         <v>9.63</v>
@@ -39671,7 +39667,7 @@
     </row>
     <row r="433" spans="1:28">
       <c r="A433" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B433">
         <v>6.76</v>
@@ -39757,7 +39753,7 @@
     </row>
     <row r="434" spans="1:28">
       <c r="A434" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B434">
         <v>9.09</v>
@@ -39843,7 +39839,7 @@
     </row>
     <row r="435" spans="1:28">
       <c r="A435" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B435">
         <v>6.5</v>
@@ -39929,7 +39925,7 @@
     </row>
     <row r="436" spans="1:28">
       <c r="A436" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B436">
         <v>7.83</v>
@@ -40015,7 +40011,7 @@
     </row>
     <row r="437" spans="1:28">
       <c r="A437" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B437">
         <v>7.28</v>
@@ -40101,7 +40097,7 @@
     </row>
     <row r="438" spans="1:28">
       <c r="A438" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B438">
         <v>8.43</v>
@@ -40187,7 +40183,7 @@
     </row>
     <row r="439" spans="1:28">
       <c r="A439" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B439">
         <v>7.34</v>
@@ -40273,7 +40269,7 @@
     </row>
     <row r="440" spans="1:28">
       <c r="A440" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B440">
         <v>7.51</v>
@@ -40359,7 +40355,7 @@
     </row>
     <row r="441" spans="1:28">
       <c r="A441" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B441">
         <v>3.84</v>
@@ -40445,7 +40441,7 @@
     </row>
     <row r="442" spans="1:28">
       <c r="A442" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B442">
         <v>4.65</v>
@@ -40531,7 +40527,7 @@
     </row>
     <row r="443" spans="1:28">
       <c r="A443" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B443">
         <v>12.2</v>
@@ -40617,7 +40613,7 @@
     </row>
     <row r="444" spans="1:28">
       <c r="A444" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B444">
         <v>6.82</v>
@@ -40703,7 +40699,7 @@
     </row>
     <row r="445" spans="1:28">
       <c r="A445" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B445">
         <v>6.01</v>
@@ -40789,7 +40785,7 @@
     </row>
     <row r="446" spans="1:28">
       <c r="A446" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B446">
         <v>5.63</v>
@@ -40875,7 +40871,7 @@
     </row>
     <row r="447" spans="1:28">
       <c r="A447" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B447">
         <v>7.84</v>
@@ -40961,7 +40957,7 @@
     </row>
     <row r="448" spans="1:28">
       <c r="A448" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B448">
         <v>4.4</v>
@@ -41047,7 +41043,7 @@
     </row>
     <row r="449" spans="1:28">
       <c r="A449" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B449">
         <v>8.6</v>
@@ -41133,7 +41129,7 @@
     </row>
     <row r="450" spans="1:28">
       <c r="A450" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B450">
         <v>3.14</v>
@@ -41219,7 +41215,7 @@
     </row>
     <row r="451" spans="1:28">
       <c r="A451" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B451">
         <v>6.68</v>
@@ -41305,7 +41301,7 @@
     </row>
     <row r="452" spans="1:28">
       <c r="A452" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B452">
         <v>6.92</v>
@@ -41391,7 +41387,7 @@
     </row>
     <row r="453" spans="1:28">
       <c r="A453" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B453">
         <v>5.35</v>
@@ -41477,7 +41473,7 @@
     </row>
     <row r="454" spans="1:28">
       <c r="A454" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B454">
         <v>1.84</v>
@@ -41563,7 +41559,7 @@
     </row>
     <row r="455" spans="1:28">
       <c r="A455" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B455">
         <v>5.64</v>
@@ -41649,7 +41645,7 @@
     </row>
     <row r="456" spans="1:28">
       <c r="A456" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B456">
         <v>4.36</v>
@@ -41735,7 +41731,7 @@
     </row>
     <row r="457" spans="1:28">
       <c r="A457" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B457">
         <v>7.85</v>
@@ -41821,7 +41817,7 @@
     </row>
     <row r="458" spans="1:28">
       <c r="A458" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B458">
         <v>2.11</v>
@@ -41907,7 +41903,7 @@
     </row>
     <row r="459" spans="1:28">
       <c r="A459" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B459">
         <v>6.14</v>
@@ -41993,7 +41989,7 @@
     </row>
     <row r="460" spans="1:28">
       <c r="A460" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B460">
         <v>5.01</v>
@@ -42079,7 +42075,7 @@
     </row>
     <row r="461" spans="1:28">
       <c r="A461" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B461">
         <v>6.53</v>
@@ -42165,7 +42161,7 @@
     </row>
     <row r="462" spans="1:28">
       <c r="A462" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B462">
         <v>3.78</v>
@@ -42251,7 +42247,7 @@
     </row>
     <row r="463" spans="1:28">
       <c r="A463" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B463">
         <v>3.44</v>
@@ -42337,7 +42333,7 @@
     </row>
     <row r="464" spans="1:28">
       <c r="A464" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B464">
         <v>8.21</v>
@@ -42423,7 +42419,7 @@
     </row>
     <row r="465" spans="1:28">
       <c r="A465" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B465">
         <v>6.92</v>
@@ -42509,7 +42505,7 @@
     </row>
     <row r="466" spans="1:28">
       <c r="A466" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B466">
         <v>3.85</v>
@@ -42595,7 +42591,7 @@
     </row>
     <row r="467" spans="1:28">
       <c r="A467" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B467">
         <v>6.56</v>
@@ -42681,7 +42677,7 @@
     </row>
     <row r="468" spans="1:28">
       <c r="A468" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B468">
         <v>7.78</v>
@@ -42767,7 +42763,7 @@
     </row>
     <row r="469" spans="1:28">
       <c r="A469" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B469">
         <v>7.35</v>
@@ -42853,7 +42849,7 @@
     </row>
     <row r="470" spans="1:28">
       <c r="A470" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B470">
         <v>7.63</v>
